--- a/output/pdf_financials_xlsx/GENM.xlsx
+++ b/output/pdf_financials_xlsx/GENM.xlsx
@@ -3062,13 +3062,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.8390069999999999</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>4.521479</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.664776</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>0</v>
@@ -6521,7 +6521,11 @@
           <t>Reserve for warrants (note 11)</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -7720,7 +7724,11 @@
           <t>RESERVE FOR WARRANTS (note 11 b)</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E69" s="5" t="n">
         <v>0.8390069999999999</v>
       </c>
@@ -8417,7 +8425,11 @@
           <t>RESERVE FOR WARRANTS (note 9 b)) 839,007</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GENM.xlsx
+++ b/output/pdf_financials_xlsx/GENM.xlsx
@@ -735,16 +735,16 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.026145</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.253659</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.435296</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.670409</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -1213,16 +1213,16 @@
         <v>-1.492819</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-17.083412</v>
+        <v>-17.109557</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-17.083412</v>
+        <v>-17.337071</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-17.763257</v>
+        <v>-18.198553</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-21.62012</v>
+        <v>-22.290529</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-21.62012</v>
@@ -1269,16 +1269,16 @@
         <v>-1.492819</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-17.083412</v>
+        <v>-17.109557</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-17.083412</v>
+        <v>-17.337071</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-17.763257</v>
+        <v>-18.198553</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-21.62012</v>
+        <v>-22.290529</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-21.62012</v>
@@ -1410,10 +1410,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.167899</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.218516</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>5.397171</v>
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>1.50255</v>
+        <v>2.670449</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.256638</v>
+        <v>1.475154</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>6.639171</v>
@@ -1802,10 +1802,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.217125</v>
+        <v>0.049226</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.252203</v>
+        <v>0.033687</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.100311</v>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E75" s="5" t="n">
@@ -15824,7 +15824,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">

--- a/output/pdf_financials_xlsx/GENM.xlsx
+++ b/output/pdf_financials_xlsx/GENM.xlsx
@@ -645,25 +645,25 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>0.062274</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>0.111423</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
+        <v>0.148404</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>0.108978</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0</v>
+        <v>0.111318</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0</v>
+        <v>0.08892899999999999</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0</v>
+        <v>0.088003</v>
       </c>
     </row>
     <row r="10">
@@ -676,7 +676,7 @@
         <v>1.596514</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.597177</v>
+        <v>0.7086</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>17.296322</v>
@@ -1238,22 +1238,22 @@
         <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.027608</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.041412</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>1.621893</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>1.410762</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>0.284026</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>0.09102499999999999</v>
       </c>
     </row>
     <row r="29">
@@ -1266,22 +1266,22 @@
         <v>-1.492819</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.492819</v>
+        <v>-1.465211</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-17.109557</v>
+        <v>-17.068145</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-17.337071</v>
+        <v>-15.715178</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-18.198553</v>
+        <v>-16.787791</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-22.290529</v>
+        <v>-22.006503</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-21.62012</v>
+        <v>-21.529095</v>
       </c>
     </row>
     <row r="30">
@@ -3268,22 +3268,22 @@
         <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.027608</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.041412</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>1.621893</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>1.410762</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.284026</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.09102499999999999</v>
       </c>
     </row>
     <row r="101">
@@ -9049,7 +9049,11 @@
           <t>Depreciation of right of use asset (note 9)</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -10215,7 +10219,11 @@
           <t>Depreciation of right of use asset (note 9)</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -11029,7 +11037,11 @@
           <t>Depreciation of right of use asset (note 10)</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -11829,7 +11841,11 @@
           <t>Depreciation of right of use asset</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -12643,7 +12659,11 @@
           <t>Depreciation of right of use asset</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -14524,7 +14544,11 @@
           <t>Occupancy cost (note 9)</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -16693,7 +16717,11 @@
           <t>Occupancy cost (note 10)</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
@@ -18321,7 +18349,11 @@
           <t>Occupancy cost (note 9)</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E278" s="5" t="n">
         <v>0.062274</v>
       </c>
@@ -20212,7 +20244,11 @@
           <t>Occupancy cost</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E315" s="5" t="n">
         <v>0.062274</v>
       </c>

--- a/output/pdf_financials_xlsx/GENM.xlsx
+++ b/output/pdf_financials_xlsx/GENM.xlsx
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-1.492819</v>
+        <v>-1.389124</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-1.492819</v>
+        <v>-1.363208</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-17.083412</v>
@@ -869,10 +869,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.103695</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.129611</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.492819</v>
+        <v>-1.389124</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.492819</v>
+        <v>-1.363208</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-17.109557</v>
@@ -1263,10 +1263,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.492819</v>
+        <v>-1.389124</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.465211</v>
+        <v>-1.3356</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-17.068145</v>
@@ -1333,10 +1333,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-0</v>
+        <v>-7.46477636265733</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>-9.50779338149424</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -3582,13 +3582,13 @@
         <v>0</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.040586</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.023517</v>
       </c>
       <c r="H111" s="3" t="n">
         <v>0</v>
@@ -3691,7 +3691,7 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>1.51359</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
@@ -4242,13 +4242,13 @@
         <v>0</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.040586</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.023517</v>
       </c>
       <c r="H134" s="3" t="n">
         <v>0</v>
@@ -4272,13 +4272,13 @@
         <v>-14.528662</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-30.822875</v>
+        <v>-30.863461</v>
       </c>
       <c r="F135" s="3" t="n">
         <v>-16.064453</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-10.179651</v>
+        <v>-10.203168</v>
       </c>
       <c r="H135" s="3" t="n">
         <v>-6.469548</v>
@@ -9425,7 +9425,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -10470,7 +10474,11 @@
           <t>Purchase of equipment (note 7)</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -11543,7 +11551,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -11592,7 +11604,11 @@
           <t>Cash at end of the year $</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -11994,7 +12010,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -12412,7 +12432,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E161" s="5" t="n">
         <v>-0.103695</v>
       </c>
@@ -18655,7 +18679,11 @@
           <t>Deferred income tax recovery (note 13 and 14)</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E284" s="5" t="n">
         <v>0.103695</v>
       </c>
@@ -20456,7 +20484,11 @@
           <t>Deferred income tax recovery (note 11 and 12)</t>
         </is>
       </c>
-      <c r="D319" t="inlineStr"/>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E319" s="5" t="n">
         <v>0.103695</v>
       </c>
